--- a/outputs/metrics/baseline_threshold_recommendations_from_validation.xlsx
+++ b/outputs/metrics/baseline_threshold_recommendations_from_validation.xlsx
@@ -558,31 +558,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6196721311475409</v>
+        <v>0.6178861788617886</v>
       </c>
       <c r="D4" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4489311163895487</v>
+        <v>0.4470588235294118</v>
       </c>
       <c r="F4" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="G4" t="n">
         <v>0.7592592592592593</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4938271604938271</v>
+        <v>0.5</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6074074074074074</v>
+        <v>0.6029411764705882</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7026647966339411</v>
+        <v>0.697054698457223</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
